--- a/AAII_Financials/Yearly/AVXL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AVXL_YR_FIN.xlsx
@@ -906,13 +906,13 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>36800</v>
+        <v>36900</v>
       </c>
       <c r="E12" s="3">
-        <v>39400</v>
+        <v>39500</v>
       </c>
       <c r="F12" s="3">
-        <v>40900</v>
+        <v>41000</v>
       </c>
       <c r="G12" s="3">
         <v>34500</v>
@@ -3023,13 +3023,13 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="E59" s="3">
-        <v>800</v>
+        <v>1400</v>
       </c>
       <c r="F59" s="3">
-        <v>900</v>
+        <v>2200</v>
       </c>
       <c r="G59" s="3">
         <v>400</v>
